--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486877_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486877_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1211</v>
+        <v>5.7752</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8639</v>
+        <v>4.5772</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2573</v>
+        <v>1.198</v>
       </c>
       <c r="G2" t="n">
         <v>2.2392</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>2.227</v>
+        <v>1.881</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7355</v>
+        <v>1.4488</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4915</v>
+        <v>0.4322</v>
       </c>
       <c r="V2" t="n">
         <v>2.271</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.931</v>
+        <v>2.2468</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2257</v>
+        <v>1.4875</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7053</v>
+        <v>0.7593</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5379</v>
+        <v>-1.8101</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8743</v>
+        <v>-0.3763</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3364</v>
+        <v>-1.4338</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4499</v>
+        <v>-0.3087</v>
       </c>
       <c r="K3" t="n">
-        <v>3.371</v>
+        <v>0.4545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0789</v>
+        <v>-0.7633</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9121</v>
+        <v>-1.5014</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4967</v>
+        <v>-0.8308</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4154</v>
+        <v>-0.6706</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.2855</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.1336</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3911</v>
+        <v>0.6791</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>0.3137</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0711</v>
+        <v>0.3653</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2875</v>
+        <v>3.9938</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>3.5359</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6982</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5302</v>
+        <v>2.1943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8599</v>
+        <v>2.4115</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6704</v>
+        <v>-0.2172</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8101</v>
+        <v>0.3268</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3763</v>
+        <v>1.3526</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4338</v>
+        <v>-1.0257</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3087</v>
+        <v>2.6673</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4545</v>
+        <v>2.6279</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7633</v>
+        <v>0.0395</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5014</v>
+        <v>-2.3405</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8308</v>
+        <v>-1.2753</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6706</v>
+        <v>-1.0652</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0375</v>
+        <v>1.2166</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3139</v>
+        <v>0.5306</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2764</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>3.9938</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5359</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2258</v>
+        <v>2.0983</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4429</v>
+        <v>0.3042</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2172</v>
+        <v>1.7942</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3268</v>
+        <v>2.5379</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3526</v>
+        <v>2.8743</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0257</v>
+        <v>-0.3364</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6673</v>
+        <v>3.4499</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6279</v>
+        <v>3.371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>0.0789</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3405</v>
+        <v>-0.9121</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2753</v>
+        <v>-0.4967</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0652</v>
+        <v>-0.4154</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4107</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-5.1336</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.248</v>
+        <v>1.5585</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4379</v>
+        <v>1.3985</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2402</v>
+        <v>1.2875</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4067</v>
+        <v>-0.5799</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0838</v>
+        <v>-0.9079</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6771</v>
+        <v>0.328</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.439</v>
+        <v>-1.1363</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8366</v>
+        <v>-0.7654</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.3709</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5465</v>
+        <v>-1.0653</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9442</v>
+        <v>-0.6943</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.3709</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0777</v>
+        <v>0.618</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7627</v>
+        <v>0.1898</v>
       </c>
       <c r="U6" t="n">
-        <v>0.315</v>
+        <v>0.4282</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5893</v>
+        <v>0.3491</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0.3491</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.953</v>
+        <v>-0.6937</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2218</v>
+        <v>-0.1056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2687</v>
+        <v>-0.5881</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1363</v>
+        <v>-1.439</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7654</v>
+        <v>-0.8366</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3709</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0653</v>
+        <v>-1.5465</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6943</v>
+        <v>-0.9442</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3709</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2449</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.124</v>
+        <v>0.5733</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3689</v>
+        <v>0.404</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3491</v>
+        <v>0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
         <v>0.3491</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5992</v>
+        <v>-1.5242</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.8707</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6239</v>
+        <v>-0.6536</v>
       </c>
       <c r="G8" t="n">
         <v>0.3702</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1747</v>
+        <v>-0.0997</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1088</v>
+        <v>-0.1385</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ORTEGA MORA</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1089</v>
+        <v>-1.6432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0784</v>
+        <v>-0.893</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1873</v>
+        <v>-0.7502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4416</v>
+        <v>-4.4066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1232</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3184</v>
+        <v>-3.6994</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0784</v>
+        <v>-1.5557</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0389</v>
+        <v>0.7076</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0395</v>
+        <v>-2.2633</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3632</v>
+        <v>-2.8509</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0843</v>
+        <v>-1.4148</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2789</v>
+        <v>-1.4361</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.2588</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.5313</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.1001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.2053</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.3986</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.3986</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-2.3573</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>J. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7287</v>
+        <v>-1.9747</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6524</v>
+        <v>0.183</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0763</v>
+        <v>-2.1577</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4066</v>
+        <v>0.4416</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0.1232</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6994</v>
+        <v>0.3184</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5557</v>
+        <v>0.0784</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7076</v>
+        <v>0.0389</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2633</v>
+        <v>0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8509</v>
+        <v>0.3632</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4148</v>
+        <v>0.0843</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4361</v>
+        <v>0.2789</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2588</v>
+        <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4459</v>
+        <v>-0.2644</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3408</v>
+        <v>0.1046</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1051</v>
+        <v>-0.369</v>
       </c>
       <c r="V10" t="n">
+        <v>-2.3573</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="n">
-        <v>0.5893</v>
-      </c>
       <c r="X10" t="n">
-        <v>-0.5893</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7646</v>
+        <v>-3.1797</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3754</v>
+        <v>-3.1977</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6108</v>
+        <v>0.018</v>
       </c>
       <c r="G11" t="n">
         <v>-5.005</v>
@@ -1312,13 +1312,13 @@
         <v>2.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5073</v>
+        <v>2.0923</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2907</v>
+        <v>0.887</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7981</v>
+        <v>1.2052</v>
       </c>
       <c r="V11" t="n">
         <v>0.3491</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.060399999999999</v>
+        <v>2.719200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3297</v>
+        <v>2.988499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2692999999999999</v>
+        <v>-0.2693000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-7.8813</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6022</v>
+        <v>3.602199999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-11.4833</v>
@@ -1375,7 +1375,7 @@
         <v>-14.1209</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.4536</v>
+        <v>-8.453600000000002</v>
       </c>
       <c r="O12" t="n">
         <v>-5.6671</v>
@@ -1390,19 +1390,19 @@
         <v>13.3472</v>
       </c>
       <c r="S12" t="n">
-        <v>9.5311</v>
+        <v>10.19</v>
       </c>
       <c r="T12" t="n">
-        <v>5.9266</v>
+        <v>6.585100000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6047</v>
+        <v>3.6046</v>
       </c>
       <c r="V12" t="n">
         <v>5.5441</v>
       </c>
       <c r="W12" t="n">
-        <v>8.644499999999999</v>
+        <v>8.644500000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-3.1004</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6601</v>
+        <v>2.838</v>
       </c>
       <c r="E13" t="n">
-        <v>2.748</v>
+        <v>2.3296</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.5083</v>
       </c>
       <c r="G13" t="n">
         <v>2.7552</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1217</v>
+        <v>0.0561</v>
       </c>
       <c r="T13" t="n">
-        <v>0.736</v>
+        <v>0.3176</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8577</v>
+        <v>-0.2615</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5893</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.6236</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7082</v>
+        <v>-0.6311</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0736</v>
+        <v>2.2547</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7072</v>
+        <v>2.8599</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5336</v>
+        <v>-1.7549</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1736</v>
+        <v>4.6148</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4798</v>
+        <v>3.6081</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2825</v>
+        <v>0.0171</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1973</v>
+        <v>3.591</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7726</v>
+        <v>-0.7482</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7489</v>
+        <v>-1.772</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.0238</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>3.2855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1143</v>
+        <v>-1.0926</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6042</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.49</v>
+        <v>-0.2826</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.1868</v>
+        <v>-0.3491</v>
       </c>
       <c r="W14" t="n">
         <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4984</v>
+        <v>0.4879</v>
       </c>
       <c r="E15" t="n">
-        <v>2.245</v>
+        <v>-2.0363</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7466</v>
+        <v>2.5242</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.517</v>
+        <v>-2.2738</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1224</v>
+        <v>-2.3945</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3947</v>
+        <v>0.1207</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.8858</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.1222</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.388</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4445</v>
+        <v>-1.2723</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3947</v>
+        <v>0.8843</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4107</v>
+        <v>2.2588</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>3.2855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4261</v>
+        <v>-0.5444</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5656</v>
+        <v>-0.3024</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1395</v>
+        <v>-0.2419</v>
       </c>
       <c r="V15" t="n">
+        <v>1.0472</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.1786</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.3573</v>
-      </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>-0.1314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2822</v>
+        <v>0.3594</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7225</v>
+        <v>0.4392</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0047</v>
+        <v>-0.0798</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2738</v>
+        <v>1.8554</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3945</v>
+        <v>-0.3992</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1207</v>
+        <v>2.2545</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8858</v>
+        <v>2.5989</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1222</v>
+        <v>1.5996</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7635999999999999</v>
+        <v>0.9993</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.388</v>
+        <v>-0.7435</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2723</v>
+        <v>-1.9988</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8843</v>
+        <v>1.2552</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2855</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.75</v>
+        <v>-1.0093</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0114</v>
+        <v>-1.0036</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7614</v>
+        <v>-0.0057</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0472</v>
+        <v>-2.3347</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>-1.1561</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1314</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.208</v>
+        <v>0.2892</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4679</v>
+        <v>2.0358</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6759</v>
+        <v>-1.7466</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8599</v>
+        <v>-1.517</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7549</v>
+        <v>-1.1224</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6148</v>
+        <v>-0.3947</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6081</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0171</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>3.591</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7482</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.772</v>
+        <v>-0.4445</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0238</v>
+        <v>-0.3947</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2855</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5082</v>
+        <v>0.2169</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6468</v>
+        <v>0.3564</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.1395</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>2.3573</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0346</v>
+        <v>0.0331</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1254</v>
+        <v>2.976</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.16</v>
+        <v>-2.9429</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8554</v>
+        <v>3.7072</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3992</v>
+        <v>2.5336</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2545</v>
+        <v>1.1736</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5989</v>
+        <v>4.4798</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5996</v>
+        <v>4.2825</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9993</v>
+        <v>0.1973</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7435</v>
+        <v>-0.7726</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9988</v>
+        <v>-1.7489</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2552</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4033</v>
+        <v>-0.4872</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3174</v>
+        <v>-0.128</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0859</v>
+        <v>-0.3593</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3347</v>
+        <v>-3.1868</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.1561</v>
+        <v>-0.3491</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0397</v>
+        <v>-0.3284</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0544</v>
+        <v>0.2594</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5878</v>
       </c>
       <c r="G19" t="n">
         <v>3.0544</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2379</v>
+        <v>-1.5265</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3174</v>
+        <v>-1.0036</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9204</v>
+        <v>-0.5229</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8295</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3247</v>
+        <v>-0.9274</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8502</v>
+        <v>-1.6564</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4745</v>
+        <v>0.7291</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4697</v>
+        <v>-1.4998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.467</v>
+        <v>-0.1495</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0027</v>
+        <v>-1.3502</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1379</v>
+        <v>-1.4161</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0195</v>
+        <v>0.0973</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1184</v>
+        <v>-1.5135</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3318</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4475</v>
+        <v>-0.2468</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1157</v>
+        <v>0.1632</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2321</v>
+        <v>1.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8566</v>
+        <v>-0.4194</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0653</v>
+        <v>-0.2403</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2088</v>
+        <v>-0.1791</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7938</v>
+        <v>-1.0961</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0749</v>
+        <v>-1.7598</v>
       </c>
       <c r="F21" t="n">
-        <v>0.281</v>
+        <v>0.6637</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4998</v>
+        <v>-1.5298</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1495</v>
+        <v>-3.7081</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3502</v>
+        <v>2.1783</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4161</v>
+        <v>0.1341</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0973</v>
+        <v>-0.9046</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5135</v>
+        <v>1.0388</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-1.664</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2468</v>
+        <v>-2.8035</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1632</v>
+        <v>1.1395</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q21" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.8748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.5663</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.0192</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.5471</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.2859</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.6587</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.6272</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.2402</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1509</v>
+        <v>-1.8529</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3875</v>
+        <v>-1.687</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2366</v>
+        <v>-0.1659</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5298</v>
+        <v>0.4697</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.7081</v>
+        <v>0.467</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1783</v>
+        <v>0.0027</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1341</v>
+        <v>0.1379</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9046</v>
+        <v>0.0195</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0388</v>
+        <v>0.1184</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.664</v>
+        <v>0.3318</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.8035</v>
+        <v>0.4475</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1395</v>
+        <v>-0.1157</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8748</v>
+        <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6211</v>
+        <v>0.3283</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6468</v>
+        <v>0.2285</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.0998</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1786</v>
+        <v>-1.4189</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0604</v>
+        <v>1.426399999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2692000000000001</v>
+        <v>0.2693999999999996</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.329799999999999</v>
+        <v>1.157</v>
       </c>
       <c r="G23" t="n">
         <v>7.881399999999999</v>
@@ -2227,7 +2227,7 @@
         <v>8.4536</v>
       </c>
       <c r="L23" t="n">
-        <v>5.667</v>
+        <v>5.667000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-6.239499999999999</v>
@@ -2248,13 +2248,13 @@
         <v>18.4809</v>
       </c>
       <c r="S23" t="n">
-        <v>-9.531099999999999</v>
+        <v>-6.0444</v>
       </c>
       <c r="T23" t="n">
         <v>-3.6046</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.926600000000001</v>
+        <v>-2.4398</v>
       </c>
       <c r="V23" t="n">
         <v>-5.544099999999999</v>
@@ -2263,7 +2263,7 @@
         <v>3.1004</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.644499999999999</v>
+        <v>-8.644500000000001</v>
       </c>
     </row>
   </sheetData>
